--- a/docker/n8n/templates/expense_template_v3.xlsx
+++ b/docker/n8n/templates/expense_template_v3.xlsx
@@ -7,14 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="経費精算書" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="タクシー利用明細" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="仮払い精算" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="区分マスタ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="記入要領" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Expense Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rideshare Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cash Advance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Categories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Instructions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'経費精算書'!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Expense Report'!$1:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="¥#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -34,58 +34,58 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <color rgb="00595959"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <color rgb="00808080"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -150,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,7 +173,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,7 +182,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,12 +223,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -621,31 +615,31 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>経費精算書（Expense Reimbursement Form）</t>
+          <t>Expense Reimbursement Form</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>様式番号: F-001-v3 ／ 準拠規程: DL-HR-RG-2024-007（第3版・2024年10月1日改訂）</t>
+          <t>Form No. F-001-v3 / Governing policy: DL-HR-RG-2024-007 (Revision 3, revised October 1, 2024)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>申請日</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>05/26/2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>精算番号</t>
+          <t>Report No.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -657,17 +651,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>氏名</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>山田 太郎</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>社員番号</t>
+          <t>Employee ID</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -679,44 +673,44 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>所属部門</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>営業本部 第一営業部</t>
+          <t>Sales, Enterprise Accounts</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>役職</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>Account Manager</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>対象期間</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026/05/01 ～ 2026/05/25</t>
+          <t>05/01/2026 – 05/25/2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>支払希望日</t>
+          <t>Payment date</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026/06/25（給与振込日）</t>
+          <t>06/25/2026 (payroll date)</t>
         </is>
       </c>
     </row>
@@ -728,42 +722,42 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>利用日</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>区分</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>件名・目的</t>
+          <t>Description / purpose</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>利用区間／場所</t>
+          <t>Route / location</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>同行者・参加者</t>
+          <t>Attendees / co-riders</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>金額（税込）</t>
+          <t>Amount (USD)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>領収書</t>
+          <t>Receipt</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>備考（F-021等）</t>
+          <t>Notes (F-021, etc.)</t>
         </is>
       </c>
     </row>
@@ -773,22 +767,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>電車</t>
+          <t>Rail</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>クライアントA社訪問</t>
+          <t>Client visit, Acme Corp</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>東京 → 横浜（往復）</t>
+          <t>Philadelphia ↔ New York (round trip)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -797,11 +791,11 @@
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>1540</v>
+        <v>186</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr"/>
@@ -812,22 +806,22 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>2026/05/10</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>タクシー（夜間）</t>
+          <t>Rideshare (late night)</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>終電後の業務終了に伴う帰宅</t>
+          <t>Ride home after work ended late</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>渋谷オフィス → 自宅（世田谷区）</t>
+          <t>Office (Midtown) → Home (Queens)</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -836,16 +830,16 @@
         </is>
       </c>
       <c r="G11" s="11" t="n">
-        <v>4820</v>
+        <v>48.2</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>業務終了 23:45 / 終電後</t>
+          <t>Work ended 11:45 PM / after last train</t>
         </is>
       </c>
     </row>
@@ -855,40 +849,40 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>05/14/2026</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>タクシー（昼間）</t>
+          <t>Rideshare (daytime)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>クライアント同席の重要書類運搬</t>
+          <t>Carrying original contracts with client</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>本社 → 大手町（B社）</t>
+          <t>HQ → Beta Inc. (Financial District)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>B社 鈴木様 同乗</t>
+          <t>Ms. Lee (Beta Inc.) rode along</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>3180</v>
+        <v>31.8</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>事前申請: 2026/05/12 承認済</t>
+          <t>Pre-approved 05/12/2026</t>
         </is>
       </c>
     </row>
@@ -898,22 +892,22 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>2026/05/16</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>新幹線</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>大阪支店との合同会議</t>
+          <t>Joint meeting with Chicago branch</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>東京 → 新大阪（普通車指定席）</t>
+          <t>LGA → ORD (economy)</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -922,11 +916,11 @@
         </is>
       </c>
       <c r="G13" s="11" t="n">
-        <v>14720</v>
+        <v>247.3</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr"/>
@@ -937,22 +931,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2026/05/16</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>宿泊費</t>
+          <t>Lodging</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>出張に伴う宿泊（大阪市）</t>
+          <t>Business trip lodging (Chicago)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>大阪市内 ホテルABC</t>
+          <t>Hotel ABC, Chicago</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -961,16 +955,16 @@
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>11500</v>
+        <v>205</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>上限13,000円以内</t>
+          <t>Within USD 220 cap</t>
         </is>
       </c>
     </row>
@@ -980,22 +974,22 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>05/18/2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>タクシー（夜間）</t>
+          <t>Rideshare (late night)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>深夜帰宅（業務終了 24:30）</t>
+          <t>Ride home (work ended 12:30 AM)</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>本社 → 自宅（練馬区）</t>
+          <t>HQ → Home (Westchester)</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -1004,16 +998,16 @@
         </is>
       </c>
       <c r="G15" s="11" t="n">
-        <v>16240</v>
+        <v>132.4</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>上限超過: F-021提出済（部長・総務部長承認）</t>
+          <t>Over cap: F-021 submitted (dept head + People Ops approval)</t>
         </is>
       </c>
     </row>
@@ -1023,40 +1017,40 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>05/20/2026</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>接待交際費</t>
+          <t>Client entertainment</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>新規開拓 C社 役員との会食</t>
+          <t>Dinner with Gamma Co. executives</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>銀座 居酒屋XYZ</t>
+          <t>Restaurant XYZ, Manhattan</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>C社 田中部長／C社 佐々木課長／当社 山田</t>
+          <t>Mr. Tanaka, Ms. Park (Gamma Co.); J. Smith</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>28600</v>
+        <v>286</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>F-009 事前申請済 / 1名@7,150円</t>
+          <t>F-009 pre-approved / USD 95.33 per person</t>
         </is>
       </c>
     </row>
@@ -1066,17 +1060,17 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>05/22/2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>消耗品</t>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>プリンタートナー購入</t>
+          <t>Printer toner</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -1090,16 +1084,16 @@
         </is>
       </c>
       <c r="G17" s="11" t="n">
-        <v>4180</v>
+        <v>41.8</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Web明細スクショ添付</t>
+          <t>Online order screenshot attached</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1103,22 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2026/05/24</t>
+          <t>05/24/2026</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>電車</t>
+          <t>Public transit</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>総務会議出席</t>
+          <t>People Operations meeting</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>東京 → 品川（往復）</t>
+          <t>Subway (round trip)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1133,7 +1127,7 @@
         </is>
       </c>
       <c r="G18" s="8" t="n">
-        <v>560</v>
+        <v>5.8</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
@@ -1142,7 +1136,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3,000円未満のため明細スクショ</t>
+          <t>Under USD 25: statement screenshot</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1299,7 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>合計（税込）／Total</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G32" s="13">
@@ -1317,7 +1311,7 @@
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>仮払金（既受領分）／Cash Advance Received</t>
+          <t>Cash advance received</t>
         </is>
       </c>
       <c r="G33" s="16" t="n">
@@ -1328,7 +1322,7 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>差引精算額（会社負担）／Net Reimbursement</t>
+          <t>Net reimbursement</t>
         </is>
       </c>
       <c r="G34" s="19">
@@ -1340,27 +1334,27 @@
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
         <is>
-          <t>申請者</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>直属上長</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>部門長</t>
+          <t>Department head</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
-          <t>経理部</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
         <is>
-          <t>総務部</t>
+          <t>People Operations</t>
         </is>
       </c>
     </row>
@@ -1374,34 +1368,34 @@
     <row r="38">
       <c r="A38" s="23" t="inlineStr">
         <is>
-          <t>（日付）</t>
+          <t>(date)</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>（日付）</t>
+          <t>(date)</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>（日付）</t>
+          <t>(date)</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>（日付）</t>
+          <t>(date)</t>
         </is>
       </c>
       <c r="H38" s="23" t="inlineStr">
         <is>
-          <t>（日付）</t>
+          <t>(date)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>※ 本書の提出期限は毎月25日17:00必着（規程第8条）。遅延の場合は翌々月精算となり、F-007 経費精算遅延始末書の添付が必要です。タクシー上限15,000円超過分は F-021 タクシー代超過利用理由書を添付してください（規程第5条第4項）。</t>
+          <t>* Reports must be received by 5:00 PM on the 25th of each month (Article 8). Late reports are reimbursed in the month after next and require a Late Submission Explanation (F-007). For rideshare/taxi fares above the USD 100 per-ride cap, attach the Excess Justification Form F-021 (Article 5, Clause 4).</t>
         </is>
       </c>
     </row>
@@ -1441,11 +1435,11 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C10:C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="区分エラー" error="区分マスタから選択してください" type="list">
-      <formula1>"電車,新幹線,飛行機,バス,タクシー（昼間）,タクシー（夜間）,自家用車,宿泊費,接待交際費,会議費,消耗品,通信費,その他"</formula1>
+    <dataValidation sqref="C10:C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Choose a category from the Categories sheet" type="list">
+      <formula1>"Public transit,Rail,Air,Bus,Rideshare (daytime),Rideshare (late night),Personal vehicle,Lodging,Client entertainment,Meetings,Supplies,Phone &amp; internet,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="H10:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"○,—,電子明細,後日提出"</formula1>
+      <formula1>"Yes,—,E-statement,To follow"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1478,14 +1472,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>タクシー利用明細（規程第5条 詳細記録）</t>
+          <t>Rideshare and Taxi Log (Article 5 detail)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>夜間（23:00以降または終電後）／クライアント同席（事前申請必須）／不可抗力 のいずれかに該当する利用のみ会社負担。上限 15,000円/回。超過分は F-021 を提出のこと。</t>
+          <t>Reimbursed only for late-night rides (after 11:00 PM or after the last train), rides with a client present (pre-approval required) or unavoidable circumstances. Cap: USD 100 per ride. Submit F-021 for any amount above the cap.</t>
         </is>
       </c>
     </row>
@@ -1497,47 +1491,47 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>利用日</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>乗車時刻</t>
+          <t>Pickup time</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>降車時刻</t>
+          <t>Drop-off time</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>乗車地</t>
+          <t>Pickup location</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>降車地</t>
+          <t>Drop-off location</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>利用目的</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>金額（税込）</t>
+          <t>Amount (USD)</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>上限超過</t>
+          <t>Over cap</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>F-021 / 事前申請 ステータス</t>
+          <t>F-021 / pre-approval status</t>
         </is>
       </c>
     </row>
@@ -1547,40 +1541,40 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>2026/05/10</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>11:50 PM</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>00:18</t>
+          <t>12:18 AM</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>渋谷オフィス（東京都渋谷区）</t>
+          <t>Office (Midtown Manhattan)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>自宅（世田谷区上馬）</t>
+          <t>Home (Astoria, Queens)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>終電後帰宅（業務終了 23:45）</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>4820</v>
+          <t>Ride home after last train (work ended 11:45 PM)</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>48.2</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1595,45 +1589,45 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>05/14/2026</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>1:20 PM</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>1:45 PM</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>本社（中央区八重洲）</t>
+          <t>HQ (Midtown Manhattan)</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>B社（千代田区大手町）</t>
+          <t>Beta Inc. (Financial District)</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>クライアント同席・重要書類運搬</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>3180</v>
+          <t>Client present, carrying original contracts</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>31.8</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>事前申請: 2026/05/12 承認済（承認者: 高橋部長）</t>
+          <t>Pre-approved 05/12/2026 (approver: R. Taylor)</t>
         </is>
       </c>
     </row>
@@ -1643,45 +1637,45 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>05/18/2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>00:35</t>
+          <t>12:35 AM</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>1:20 AM</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>本社（中央区八重洲）</t>
+          <t>HQ (Midtown Manhattan)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>自宅（練馬区豊玉北）</t>
+          <t>Home (White Plains, Westchester)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>深夜帰宅（業務終了 24:30）</t>
-        </is>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>16240</v>
+          <t>Ride home (work ended 12:30 AM)</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>132.4</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>F-021 提出済 / 部長: 5/19承認 / 総務部長: 5/20承認</t>
+          <t>F-021 submitted / dept head approved 5/19 / People Ops approved 5/20</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1689,7 @@
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="27" t="n"/>
+      <c r="H8" s="8" t="n"/>
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="n"/>
     </row>
@@ -1709,7 +1703,7 @@
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="27" t="n"/>
+      <c r="H9" s="8" t="n"/>
       <c r="I9" s="7" t="n"/>
       <c r="J9" s="7" t="n"/>
     </row>
@@ -1723,7 +1717,7 @@
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="27" t="n"/>
+      <c r="H10" s="8" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
     </row>
@@ -1737,7 +1731,7 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="27" t="n"/>
+      <c r="H11" s="8" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
     </row>
@@ -1751,7 +1745,7 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="27" t="n"/>
+      <c r="H12" s="8" t="n"/>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="n"/>
     </row>
@@ -1765,7 +1759,7 @@
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="27" t="n"/>
+      <c r="H13" s="8" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
     </row>
@@ -1779,7 +1773,7 @@
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="27" t="n"/>
+      <c r="H14" s="8" t="n"/>
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="n"/>
     </row>
@@ -1793,7 +1787,7 @@
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="27" t="n"/>
+      <c r="H15" s="8" t="n"/>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
     </row>
@@ -1804,7 +1798,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="I5:I20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"なし,あり"</formula1>
+      <formula1>"No,Yes"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1832,14 +1826,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>仮払い精算明細（規程第12条）</t>
+          <t>Cash Advance Settlement (Article 12)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>出張等の前に仮払いを受けた場合、帰着後5営業日以内に本シートを用いて清算すること。</t>
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>If you received a cash advance before a trip, settle it on this sheet within 5 business days after return.</t>
         </is>
       </c>
     </row>
@@ -1851,32 +1845,32 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>仮払申請日</t>
+          <t>Request date</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>目的</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>仮払金額</t>
+          <t>Advance</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>実費合計</t>
+          <t>Actual total</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>差額</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -1886,9 +1880,9 @@
       </c>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27">
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8">
         <f>D5-E5</f>
         <v/>
       </c>
@@ -1900,9 +1894,9 @@
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27">
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8">
         <f>D6-E6</f>
         <v/>
       </c>
@@ -1914,9 +1908,9 @@
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27">
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8">
         <f>D7-E7</f>
         <v/>
       </c>
@@ -1928,9 +1922,9 @@
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27">
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8">
         <f>D8-E8</f>
         <v/>
       </c>
@@ -1942,9 +1936,9 @@
       </c>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27">
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8">
         <f>D9-E9</f>
         <v/>
       </c>
@@ -1956,9 +1950,9 @@
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27">
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8">
         <f>D10-E10</f>
         <v/>
       </c>
@@ -1970,9 +1964,9 @@
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27">
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8">
         <f>D11-E11</f>
         <v/>
       </c>
@@ -1984,9 +1978,9 @@
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27">
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8">
         <f>D12-E12</f>
         <v/>
       </c>
@@ -2018,199 +2012,199 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>区分名</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B1" s="21" t="inlineStr">
         <is>
-          <t>勘定科目</t>
+          <t>GL account</t>
         </is>
       </c>
       <c r="C1" s="21" t="inlineStr">
         <is>
-          <t>備考・規程参照</t>
+          <t>Notes / policy reference</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>電車</t>
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Public transit</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>規程第4条 / 経済的経路かつ最短時間</t>
+          <t>Article 4 / most economical and fastest route</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
-        <is>
-          <t>新幹線</t>
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Rail</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>規程第4条第2項 / 100km以上で普通車指定席</t>
+          <t>Article 4, Para. 2 / coach for trips of 100+ miles</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>飛行機</t>
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Air</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>規程第4条第3項 / 300km以上または2時間短縮</t>
+          <t>Article 4, Para. 3 / 300+ miles or saves 2+ hours</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>バス</t>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Bus</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>規程第4条</t>
+          <t>Article 4</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>タクシー（昼間）</t>
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Rideshare (daytime)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>規程第5条第2項 / クライアント同席等の例外のみ</t>
+          <t>Article 5, Clause 2 / exceptions only, e.g. client present</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>タクシー（夜間）</t>
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Rideshare (late night)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>規程第5条第1項 / 23:00以降または終電後</t>
+          <t>Article 5, Clause 1 / after 11:00 PM or after the last train</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>自家用車</t>
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Personal vehicle</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>規程第6条 / 1km=25円 / F-015 必須</t>
+          <t>Article 6 / USD 0.67 per mile / F-015 required</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>宿泊費</t>
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Lodging</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>旅費交通費</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>規程第7条 / 地域別上限</t>
+          <t>Article 7 / caps by location</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>接待交際費</t>
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Client entertainment</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>交際費</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>規程第10条 / 5,000円超は F-009</t>
+          <t>Article 10 / F-009 above USD 75 per person</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>会議費</t>
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>会議費</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>社内会議の弁当代等</t>
+          <t>Meals for internal meetings, etc.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>消耗品</t>
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -2220,14 +2214,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>通信費</t>
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Phone &amp; internet</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -2237,19 +2231,19 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t>その他</t>
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>雑費</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>上長承認必須</t>
+          <t>Manager approval required</t>
         </is>
       </c>
     </row>
@@ -2274,238 +2268,238 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>経費精算テンプレート_v3.xlsx 記入要領</t>
+          <t>expense_template_v3.xlsx — How to fill in</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>準拠規程: 株式会社デモ・ロジスティクス 旅費交通費・経費精算および労務手続き規定（DL-HR-RG-2024-007 第3版）</t>
+          <t>Governing policy: Demo Logistics Inc. Travel, Expense Reimbursement and HR Procedures Policy (DL-HR-RG-2024-007, Revision 3)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>【提出期限】</t>
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Submission deadline</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　毎月25日 17:00 必着（規程第8条）。</t>
+          <t>Reports must be received by 5:00 PM on the 25th of each month (Article 8).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　25日が土日祝日の場合は、直前の営業日に繰り上げ。</t>
+          <t>If the 25th falls on a weekend or holiday, the deadline moves to the preceding business day.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　期限を過ぎた場合は翌々月精算となり、F-007 経費精算遅延始末書の添付が必要。</t>
+          <t>Late reports are reimbursed in the month after next and require a Late Submission Explanation (F-007).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　年度内に3回以上遅延した場合、人事考課のコンピテンシー評価で減点対象。</t>
+          <t>Three or more late submissions in a fiscal year lead to a deduction in the performance review.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>【記入手順】</t>
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>How to fill in</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　1. 「経費精算書」シートのヘッダー欄（氏名・社員番号・所属・対象期間等）を記入。</t>
+          <t>1. Complete the header of the Expense Report sheet (name, employee ID, department, period, etc.).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　2. 明細欄に1件1行で経費を記入。「区分」はドロップダウンから選択。</t>
+          <t>2. Enter one expense per row. Choose the Category from the drop-down.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3. 領収書欄は ○（原本提出）／—（添付なし）／電子明細／後日提出 から選択。</t>
+          <t>3. In the Receipt column choose Yes (receipt attached), — (none), E-statement or To follow.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　4. タクシー利用は「タクシー利用明細」シートにも記入（規程第5条 詳細記録）。</t>
+          <t>4. Also record rideshare and taxi rides on the Rideshare Log sheet (Article 5 detail).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　5. 仮払いを受けていた場合は「仮払い精算」シートに記入。</t>
+          <t>5. If you received a cash advance, complete the Cash Advance sheet.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　6. 合計金額・差引精算額は自動計算（数式が破損しないよう、行の途中挿入は避けること）。</t>
+          <t>6. Totals and net reimbursement are calculated automatically (avoid inserting rows mid-table so the formulas stay intact).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　7. 直属上長 → 部門長 → 経理 → 総務 の順で承認印を取得。</t>
+          <t>7. Obtain approvals in this order: manager → department head → Accounts Payable → People Operations.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>【領収書の取扱い】</t>
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Receipts</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　1件3,000円以上：原則として原本領収書を必須（電子レシート PDF/JPEG も可）。</t>
+          <t>USD 25 or more: an itemized receipt is required (PDF or JPEG e-receipts are accepted).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　1件3,000円未満：利用日・店舗名・金額・利用目的が判別できる電子明細スクショで代替可。</t>
+          <t>Under USD 25: a screenshot of the electronic statement showing date, merchant, amount and purpose is accepted.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　飲食を伴う経費：参加者全員の氏名・所属を必ず明記。1人あたり5,000円超の接待は F-009 事前申請必須。</t>
+          <t>Meals: list the names and affiliations of all attendees. Client entertainment above USD 75 per person requires F-009 pre-approval.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>【タクシー代の重要ルール（規程第5条）】</t>
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Rideshare and taxi rules (Article 5)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　夜間（23:00以降）または終電後の業務終了帰宅 → 会社負担可。</t>
+          <t>Ride home after work ends after 11:00 PM, or after the last train → reimbursable.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　昼間のタクシー → 原則NG。例外は ①クライアント同席+事前申請、②重量物/機密物運搬、③不可抗力。</t>
+          <t>Daytime rides → not reimbursable as a rule. Exceptions: (1) client present + pre-approval, (2) heavy or confidential items, (3) unavoidable circumstances.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　1回 15,000円（税込）が上限。超過分は F-021 タクシー代超過利用理由書を提出（部長＋総務部長の二者承認）。</t>
+          <t>Cap: USD 100 per ride (tax and tip included). For any excess, submit the Excess Justification Form F-021 (department head + Director of People Operations).</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　F-021 の提出期限は利用日の翌々営業日 17:00 まで。それ以降は全額自己負担。</t>
+          <t>F-021 is due by 5:00 PM two business days after the ride. After that, the full fare is paid by the employee.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　私的飲食後の帰宅、自宅最寄り駅までのタクシー、観光混在の移動は会社負担対象外。</t>
+          <t>Rides home after private social events, rides to the nearest station, and trips mixed with sightseeing are not reimbursable.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>【フォーマット利用上の注意】</t>
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>Using this template</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　本テンプレートは v3 です。v2以前のフォーマットでの申請は受理されません（規程第9条第3項）。</t>
+          <t>This is template v3. Reports on v2 or older templates are not accepted (Article 9, Paragraph 3).</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　本ファイルは Google Drive 上で配布されます。原本のセル構造・数式を変更しないでください。</t>
+          <t>Macros must be enabled (Article 9, Paragraph 4). Do not change the cell structure or formulas.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　編集する場合は、ローカルにダウンロードしてから記入し、ワークフローシステム Coconala-Flow にアップロードしてください。</t>
+          <t>Download the file, fill it in locally, and upload it to the FlowDesk workflow system.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　ファイル名は「経費精算_YYYY-MM_氏名.xlsx」の形式で保存することを推奨します。</t>
+          <t>Recommended file name: Expenses_YYYY-MM_FirstLast.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="31" t="inlineStr">
-        <is>
-          <t>【お問い合わせ】</t>
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Contacts</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　経費・支払関連: 経理部 鈴木 美咲（内線 1456 / suzuki.misaki@demo-logistics.example.co.jp）</t>
+          <t>Expenses and payments: Accounts Payable (ext. 1456 / accounts-payable@demo-logistics.example.com)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　規程・労務関連: 総務部 佐藤 健一（内線 1234 / sato.kenichi@demo-logistics.example.co.jp）</t>
+          <t>Policy and HR: People Operations (ext. 1234 / people-ops@demo-logistics.example.com)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　シフト・夜勤関連: 物流部 田中 浩二（内線 2210）</t>
+          <t>Shifts and night work: Logistics Operations (ext. 2210)</t>
         </is>
       </c>
     </row>

--- a/docker/n8n/templates/expense_template_v3.xlsx
+++ b/docker/n8n/templates/expense_template_v3.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Form No. F-001-v3 / Governing policy: DL-HR-RG-2024-007 (Revision 3, revised October 1, 2024)</t>
+          <t>Form No. F-001-v3 / Governing policy: NL-HR-RG-2024-007 (Revision 3, revised October 1, 2024)</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>DL-04321</t>
+          <t>NL-04321</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Governing policy: Demo Logistics Inc. Travel, Expense Reimbursement and HR Procedures Policy (DL-HR-RG-2024-007, Revision 3)</t>
+          <t>Governing policy: Nexus Logistics, Inc. Travel, Expense Reimbursement and HR Procedures Policy (NL-HR-RG-2024-007, Revision 3)</t>
         </is>
       </c>
     </row>
@@ -2485,14 +2485,14 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Expenses and payments: Accounts Payable (ext. 1456 / accounts-payable@demo-logistics.example.com)</t>
+          <t>Expenses and payments: Accounts Payable (ext. 1456 / accounts-payable@nexus-logistics.example.com)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Policy and HR: People Operations (ext. 1234 / people-ops@demo-logistics.example.com)</t>
+          <t>Policy and HR: People Operations (ext. 1234 / people-ops@nexus-logistics.example.com)</t>
         </is>
       </c>
     </row>
